--- a/skills/agent-scrooge/assets/examples/falcon-portal/falcon-portal.xlsx
+++ b/skills/agent-scrooge/assets/examples/falcon-portal/falcon-portal.xlsx
@@ -11,19 +11,20 @@
     <sheet name="Multi-Year" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Epics" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Sprints" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Revenue" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Rate Card" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Other Costs" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Run Costs" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Dev" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Test" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Prod" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Claude Prices" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Claude Usage" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Claude Usage Detail" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Claude Usage Daily" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Project Timeline" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Sources &amp; Gaps" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Phase Budgets" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Revenue" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Rate Card" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Other Costs" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Run Costs" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Dev" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Test" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Prod" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Claude Prices" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Claude Usage" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Claude Usage Detail" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Claude Usage Daily" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Project Timeline" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Sources &amp; Gaps" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="DeliveryDays">Overall!$B$5</definedName>
@@ -259,7 +260,19 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="tblOtherCosts" displayName="tblOtherCosts" ref="A4:F9" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="tblRateCard" displayName="tblRateCard" ref="A4:C10" headerRowCount="1">
+  <autoFilter ref="A4:C10"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Role"/>
+    <tableColumn id="2" name="Day rate (USD)"/>
+    <tableColumn id="3" name="Note"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="tblOtherCosts" displayName="tblOtherCosts" ref="A4:F9" headerRowCount="1">
   <autoFilter ref="A4:F9"/>
   <tableColumns count="6">
     <tableColumn id="1" name="#"/>
@@ -273,8 +286,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="tblRunCosts" displayName="tblRunCosts" ref="A4:E9" headerRowCount="1">
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="tblRunCosts" displayName="tblRunCosts" ref="A4:E9" headerRowCount="1">
   <autoFilter ref="A4:E9"/>
   <tableColumns count="5">
     <tableColumn id="1" name="#"/>
@@ -287,8 +300,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="tblEnvDev" displayName="tblEnvDev" ref="A4:O12" headerRowCount="1">
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tblEnvDev" displayName="tblEnvDev" ref="A4:O12" headerRowCount="1">
   <autoFilter ref="A4:O12"/>
   <tableColumns count="15">
     <tableColumn id="1" name="#"/>
@@ -311,32 +324,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tblEnvTest" displayName="tblEnvTest" ref="A4:O13" headerRowCount="1">
-  <autoFilter ref="A4:O13"/>
-  <tableColumns count="15">
-    <tableColumn id="1" name="#"/>
-    <tableColumn id="2" name="Component"/>
-    <tableColumn id="3" name="Azure service"/>
-    <tableColumn id="4" name="SKU / tier"/>
-    <tableColumn id="5" name="Unit"/>
-    <tableColumn id="6" name="Unit price (USD)"/>
-    <tableColumn id="7" name="Quantity"/>
-    <tableColumn id="8" name="Usage per month"/>
-    <tableColumn id="9" name="Monthly cost (USD)"/>
-    <tableColumn id="10" name="Daily cost (USD)"/>
-    <tableColumn id="11" name="Annual cost (USD)"/>
-    <tableColumn id="12" name="Cited from"/>
-    <tableColumn id="13" name="Price source"/>
-    <tableColumn id="14" name="Note"/>
-    <tableColumn id="15" name="Environment"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
-</table>
-</file>
-
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="tblEnvProd" displayName="tblEnvProd" ref="A4:O13" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="tblEnvTest" displayName="tblEnvTest" ref="A4:O13" headerRowCount="1">
   <autoFilter ref="A4:O13"/>
   <tableColumns count="15">
     <tableColumn id="1" name="#"/>
@@ -360,7 +349,31 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="tblClaudePrices" displayName="tblClaudePrices" ref="A4:G22" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="tblEnvProd" displayName="tblEnvProd" ref="A4:O13" headerRowCount="1">
+  <autoFilter ref="A4:O13"/>
+  <tableColumns count="15">
+    <tableColumn id="1" name="#"/>
+    <tableColumn id="2" name="Component"/>
+    <tableColumn id="3" name="Azure service"/>
+    <tableColumn id="4" name="SKU / tier"/>
+    <tableColumn id="5" name="Unit"/>
+    <tableColumn id="6" name="Unit price (USD)"/>
+    <tableColumn id="7" name="Quantity"/>
+    <tableColumn id="8" name="Usage per month"/>
+    <tableColumn id="9" name="Monthly cost (USD)"/>
+    <tableColumn id="10" name="Daily cost (USD)"/>
+    <tableColumn id="11" name="Annual cost (USD)"/>
+    <tableColumn id="12" name="Cited from"/>
+    <tableColumn id="13" name="Price source"/>
+    <tableColumn id="14" name="Note"/>
+    <tableColumn id="15" name="Environment"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="tblClaudePrices" displayName="tblClaudePrices" ref="A4:G22" headerRowCount="1">
   <autoFilter ref="A4:G22"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Pricing model"/>
@@ -375,8 +388,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="tblClaudeUsage" displayName="tblClaudeUsage" ref="A4:I7" headerRowCount="1">
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="tblClaudeUsage" displayName="tblClaudeUsage" ref="A4:I7" headerRowCount="1">
   <autoFilter ref="A4:I7"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Model"/>
@@ -393,8 +406,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="tblClaudeUsageDetail" displayName="tblClaudeUsageDetail" ref="A4:P19" headerRowCount="1">
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tblClaudeUsageDetail" displayName="tblClaudeUsageDetail" ref="A4:P19" headerRowCount="1">
   <autoFilter ref="A4:P19"/>
   <tableColumns count="16">
     <tableColumn id="1" name="Kind"/>
@@ -418,8 +431,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tblClaudeUsageDaily" displayName="tblClaudeUsageDaily" ref="A4:O233" headerRowCount="1">
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tblClaudeUsageDaily" displayName="tblClaudeUsageDaily" ref="A4:O233" headerRowCount="1">
   <autoFilter ref="A4:O233"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Day"/>
@@ -442,23 +455,6 @@
 </table>
 </file>
 
-<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tblTimeline" displayName="tblTimeline" ref="A4:H20" headerRowCount="1">
-  <autoFilter ref="A4:H20"/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="Category"/>
-    <tableColumn id="2" name="Name"/>
-    <tableColumn id="3" name="Detail"/>
-    <tableColumn id="4" name="Status"/>
-    <tableColumn id="5" name="Started"/>
-    <tableColumn id="6" name="Completed"/>
-    <tableColumn id="7" name="Days"/>
-    <tableColumn id="8" name="Source"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
-</table>
-</file>
-
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblTeam" displayName="tblTeam" ref="A19:H28" headerRowCount="1">
   <autoFilter ref="A19:H28"/>
@@ -471,6 +467,23 @@
     <tableColumn id="6" name="Mandays"/>
     <tableColumn id="7" name="Cost (USD)"/>
     <tableColumn id="8" name="Cited from"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tblTimeline" displayName="tblTimeline" ref="A4:H20" headerRowCount="1">
+  <autoFilter ref="A4:H20"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Category"/>
+    <tableColumn id="2" name="Name"/>
+    <tableColumn id="3" name="Detail"/>
+    <tableColumn id="4" name="Status"/>
+    <tableColumn id="5" name="Started"/>
+    <tableColumn id="6" name="Completed"/>
+    <tableColumn id="7" name="Days"/>
+    <tableColumn id="8" name="Source"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
@@ -585,7 +598,22 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tblRevenue" displayName="tblRevenue" ref="A4:J8" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tblPhaseBudgets" displayName="tblPhaseBudgets" ref="A4:F10" headerRowCount="1">
+  <autoFilter ref="A4:F10"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="Phase"/>
+    <tableColumn id="2" name="Claude API budget (USD)"/>
+    <tableColumn id="3" name="Claude API actual (USD)"/>
+    <tableColumn id="4" name="Variance (USD)"/>
+    <tableColumn id="5" name="Variance %"/>
+    <tableColumn id="6" name="Cited from"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="tblRevenue" displayName="tblRevenue" ref="A4:J8" headerRowCount="1">
   <autoFilter ref="A4:J8"/>
   <tableColumns count="10">
     <tableColumn id="1" name="#"/>
@@ -598,18 +626,6 @@
     <tableColumn id="8" name="Year 5"/>
     <tableColumn id="9" name="Cited from"/>
     <tableColumn id="10" name="Note"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="tblRateCard" displayName="tblRateCard" ref="A4:C10" headerRowCount="1">
-  <autoFilter ref="A4:C10"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Role"/>
-    <tableColumn id="2" name="Day rate (USD)"/>
-    <tableColumn id="3" name="Note"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
@@ -1920,7 +1936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1943,7 +1959,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Test environment</t>
+          <t>Dev environment</t>
         </is>
       </c>
     </row>
@@ -2061,9 +2077,8 @@
       <c r="G5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="13">
-        <f>HoursPerMonth</f>
-        <v/>
+      <c r="H5" s="4" t="n">
+        <v>220</v>
       </c>
       <c r="I5" s="14">
         <f>F5*G5*H5*FxRate</f>
@@ -2087,10 +2102,14 @@
           <t>Azure Retail Prices API, Virtual Machines Dsv5 Series / D4s v5, uaenorth, USD per 1 Hour, meterId 75a8da05-74dd-5b32-bb86-4f5cc74cdb60, fetched 2026-09-28</t>
         </is>
       </c>
-      <c r="N5" s="25" t="inlineStr"/>
+      <c r="N5" s="25" t="inlineStr">
+        <is>
+          <t>Dev nodes stopped outside working hours</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Dev</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2172,7 @@
       <c r="N6" s="25" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Dev</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2234,7 @@
       <c r="N7" s="25" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Dev</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2296,7 @@
       <c r="N8" s="25" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Dev</t>
         </is>
       </c>
     </row>
@@ -2339,69 +2358,29 @@
       <c r="N9" s="25" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Dev</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Edge</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Azure Front Door Service</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Standard base fee</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1 Month</t>
-        </is>
-      </c>
-      <c r="F10" s="35" t="n">
-        <v>35</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="15" t="n"/>
       <c r="I10" s="14">
-        <f>F10*G10*H10*FxRate</f>
+        <f>IF(F10="","",F10*G10*H10*FxRate)</f>
         <v/>
       </c>
       <c r="J10" s="14">
-        <f>I10*12/365</f>
+        <f>IF(I10="","",I10*12/365)</f>
         <v/>
       </c>
       <c r="K10" s="14">
-        <f>I10*12</f>
-        <v/>
-      </c>
-      <c r="L10" s="25" t="inlineStr">
-        <is>
-          <t>_bmad-output/planning-artifacts/architecture/falcon/ARCHITECTURE-SPINE.md AD-4</t>
-        </is>
-      </c>
-      <c r="M10" s="25" t="inlineStr">
-        <is>
-          <t>Synthetic sample price (not looked up)</t>
-        </is>
-      </c>
-      <c r="N10" s="25" t="inlineStr"/>
+        <f>IF(I10="","",I10*12)</f>
+        <v/>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Dev</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2402,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Dev</t>
         </is>
       </c>
     </row>
@@ -2445,60 +2424,38 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Dev</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
-      <c r="H13" s="15" t="n"/>
-      <c r="I13" s="14">
-        <f>IF(F13="","",F13*G13*H13*FxRate)</f>
-        <v/>
-      </c>
-      <c r="J13" s="14">
-        <f>IF(I13="","",I13*12/365)</f>
-        <v/>
-      </c>
-      <c r="K13" s="14">
-        <f>IF(I13="","",I13*12)</f>
-        <v/>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="16" t="n"/>
-      <c r="H14" s="16" t="n"/>
-      <c r="I14" s="18">
-        <f>SUM(I5:I13)</f>
-        <v/>
-      </c>
-      <c r="J14" s="18">
-        <f>SUM(J5:J13)</f>
-        <v/>
-      </c>
-      <c r="K14" s="18">
-        <f>SUM(K5:K13)</f>
-        <v/>
-      </c>
-      <c r="L14" s="16" t="n"/>
-      <c r="M14" s="16" t="n"/>
-      <c r="N14" s="16" t="n"/>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="16" t="n"/>
+      <c r="G13" s="16" t="n"/>
+      <c r="H13" s="16" t="n"/>
+      <c r="I13" s="18">
+        <f>SUM(I5:I12)</f>
+        <v/>
+      </c>
+      <c r="J13" s="18">
+        <f>SUM(J5:J12)</f>
+        <v/>
+      </c>
+      <c r="K13" s="18">
+        <f>SUM(K5:K12)</f>
+        <v/>
+      </c>
+      <c r="L13" s="16" t="n"/>
+      <c r="M13" s="16" t="n"/>
+      <c r="N13" s="16" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2537,7 +2494,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Prod environment</t>
+          <t>Test environment</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2610,7 @@
         <v>0.235</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" s="13">
         <f>HoursPerMonth</f>
@@ -2684,7 +2641,7 @@
       <c r="N5" s="25" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Prod</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2661,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>General Purpose Gen5, 4 vCore</t>
+          <t>General Purpose Gen5, 2 vCore</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2716,7 +2673,7 @@
         <v>0.253</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H6" s="13">
         <f>HoursPerMonth</f>
@@ -2747,7 +2704,7 @@
       <c r="N6" s="25" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Prod</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2736,7 @@
         <v>0.019</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>1</v>
@@ -2798,7 +2755,7 @@
       </c>
       <c r="L7" s="25" t="inlineStr">
         <is>
-          <t>_bmad-output/planning-artifacts/architecture/falcon/ARCHITECTURE-SPINE.md AD-3</t>
+          <t>assumption: 50 GB of test documents</t>
         </is>
       </c>
       <c r="M7" s="25" t="inlineStr">
@@ -2809,7 +2766,7 @@
       <c r="N7" s="25" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Prod</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2828,7 @@
       <c r="N8" s="25" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Prod</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2860,7 @@
         <v>2.76</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>1</v>
@@ -2933,7 +2890,7 @@
       <c r="N9" s="25" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Prod</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2952,7 @@
       <c r="N10" s="25" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Prod</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -3017,7 +2974,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Prod</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -3039,7 +2996,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Prod</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3018,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Prod</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -3103,6 +3060,600 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Prod environment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Azure retail list prices (pay-as-you-go) in uaenorth, USD, fetched 2026-09-28. Daily cost is the monthly cost spread over the year (x 12 / 365). Blue cells are inputs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Azure service</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>SKU / tier</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Unit price (USD)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Usage per month</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Monthly cost (USD)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Daily cost (USD)</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Annual cost (USD)</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Cited from</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Price source</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AKS nodes</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Virtual Machines</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Standard_D4s_v5</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1 Hour</t>
+        </is>
+      </c>
+      <c r="F5" s="35" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="13">
+        <f>HoursPerMonth</f>
+        <v/>
+      </c>
+      <c r="I5" s="14">
+        <f>F5*G5*H5*FxRate</f>
+        <v/>
+      </c>
+      <c r="J5" s="14">
+        <f>I5*12/365</f>
+        <v/>
+      </c>
+      <c r="K5" s="14">
+        <f>I5*12</f>
+        <v/>
+      </c>
+      <c r="L5" s="25" t="inlineStr">
+        <is>
+          <t>_bmad-output/planning-artifacts/architecture/falcon/ARCHITECTURE-SPINE.md AD-1</t>
+        </is>
+      </c>
+      <c r="M5" s="25" t="inlineStr">
+        <is>
+          <t>Azure Retail Prices API, Virtual Machines Dsv5 Series / D4s v5, uaenorth, USD per 1 Hour, meterId 75a8da05-74dd-5b32-bb86-4f5cc74cdb60, fetched 2026-09-28</t>
+        </is>
+      </c>
+      <c r="N5" s="25" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Customer database</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SQL Database</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>General Purpose Gen5, 4 vCore</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1 vCore Hour</t>
+        </is>
+      </c>
+      <c r="F6" s="35" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" s="13">
+        <f>HoursPerMonth</f>
+        <v/>
+      </c>
+      <c r="I6" s="14">
+        <f>F6*G6*H6*FxRate</f>
+        <v/>
+      </c>
+      <c r="J6" s="14">
+        <f>I6*12/365</f>
+        <v/>
+      </c>
+      <c r="K6" s="14">
+        <f>I6*12</f>
+        <v/>
+      </c>
+      <c r="L6" s="25" t="inlineStr">
+        <is>
+          <t>_bmad-output/planning-artifacts/architecture/falcon/ARCHITECTURE-SPINE.md AD-2</t>
+        </is>
+      </c>
+      <c r="M6" s="25" t="inlineStr">
+        <is>
+          <t>Synthetic sample price (not looked up)</t>
+        </is>
+      </c>
+      <c r="N6" s="25" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Document storage</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Blob Hot LRS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1 GB/Month</t>
+        </is>
+      </c>
+      <c r="F7" s="35" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="14">
+        <f>F7*G7*H7*FxRate</f>
+        <v/>
+      </c>
+      <c r="J7" s="14">
+        <f>I7*12/365</f>
+        <v/>
+      </c>
+      <c r="K7" s="14">
+        <f>I7*12</f>
+        <v/>
+      </c>
+      <c r="L7" s="25" t="inlineStr">
+        <is>
+          <t>_bmad-output/planning-artifacts/architecture/falcon/ARCHITECTURE-SPINE.md AD-3</t>
+        </is>
+      </c>
+      <c r="M7" s="25" t="inlineStr">
+        <is>
+          <t>Synthetic sample price (not looked up)</t>
+        </is>
+      </c>
+      <c r="N7" s="25" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Secrets</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Key Vault</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>10K operations</t>
+        </is>
+      </c>
+      <c r="F8" s="35" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="14">
+        <f>F8*G8*H8*FxRate</f>
+        <v/>
+      </c>
+      <c r="J8" s="14">
+        <f>I8*12/365</f>
+        <v/>
+      </c>
+      <c r="K8" s="14">
+        <f>I8*12</f>
+        <v/>
+      </c>
+      <c r="L8" s="25" t="inlineStr">
+        <is>
+          <t>_bmad-output/planning-artifacts/architecture/falcon/ARCHITECTURE-SPINE.md AD-5</t>
+        </is>
+      </c>
+      <c r="M8" s="25" t="inlineStr">
+        <is>
+          <t>Synthetic sample price (not looked up)</t>
+        </is>
+      </c>
+      <c r="N8" s="25" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Logs and metrics</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Log Analytics</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Pay-as-you-go</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1 GB</t>
+        </is>
+      </c>
+      <c r="F9" s="35" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="14">
+        <f>F9*G9*H9*FxRate</f>
+        <v/>
+      </c>
+      <c r="J9" s="14">
+        <f>I9*12/365</f>
+        <v/>
+      </c>
+      <c r="K9" s="14">
+        <f>I9*12</f>
+        <v/>
+      </c>
+      <c r="L9" s="25" t="inlineStr">
+        <is>
+          <t>_bmad-output/planning-artifacts/architecture/falcon/ARCHITECTURE-SPINE.md AD-5</t>
+        </is>
+      </c>
+      <c r="M9" s="25" t="inlineStr">
+        <is>
+          <t>Synthetic sample price (not looked up)</t>
+        </is>
+      </c>
+      <c r="N9" s="25" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Azure Front Door Service</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Standard base fee</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1 Month</t>
+        </is>
+      </c>
+      <c r="F10" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="14">
+        <f>F10*G10*H10*FxRate</f>
+        <v/>
+      </c>
+      <c r="J10" s="14">
+        <f>I10*12/365</f>
+        <v/>
+      </c>
+      <c r="K10" s="14">
+        <f>I10*12</f>
+        <v/>
+      </c>
+      <c r="L10" s="25" t="inlineStr">
+        <is>
+          <t>_bmad-output/planning-artifacts/architecture/falcon/ARCHITECTURE-SPINE.md AD-4</t>
+        </is>
+      </c>
+      <c r="M10" s="25" t="inlineStr">
+        <is>
+          <t>Synthetic sample price (not looked up)</t>
+        </is>
+      </c>
+      <c r="N10" s="25" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="15" t="n"/>
+      <c r="I11" s="14">
+        <f>IF(F11="","",F11*G11*H11*FxRate)</f>
+        <v/>
+      </c>
+      <c r="J11" s="14">
+        <f>IF(I11="","",I11*12/365)</f>
+        <v/>
+      </c>
+      <c r="K11" s="14">
+        <f>IF(I11="","",I11*12)</f>
+        <v/>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="15" t="n"/>
+      <c r="H12" s="15" t="n"/>
+      <c r="I12" s="14">
+        <f>IF(F12="","",F12*G12*H12*FxRate)</f>
+        <v/>
+      </c>
+      <c r="J12" s="14">
+        <f>IF(I12="","",I12*12/365)</f>
+        <v/>
+      </c>
+      <c r="K12" s="14">
+        <f>IF(I12="","",I12*12)</f>
+        <v/>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="F13" s="15" t="n"/>
+      <c r="G13" s="15" t="n"/>
+      <c r="H13" s="15" t="n"/>
+      <c r="I13" s="14">
+        <f>IF(F13="","",F13*G13*H13*FxRate)</f>
+        <v/>
+      </c>
+      <c r="J13" s="14">
+        <f>IF(I13="","",I13*12/365)</f>
+        <v/>
+      </c>
+      <c r="K13" s="14">
+        <f>IF(I13="","",I13*12)</f>
+        <v/>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="16" t="n"/>
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="16" t="n"/>
+      <c r="I14" s="18">
+        <f>SUM(I5:I13)</f>
+        <v/>
+      </c>
+      <c r="J14" s="18">
+        <f>SUM(J5:J13)</f>
+        <v/>
+      </c>
+      <c r="K14" s="18">
+        <f>SUM(K5:K13)</f>
+        <v/>
+      </c>
+      <c r="L14" s="16" t="n"/>
+      <c r="M14" s="16" t="n"/>
+      <c r="N14" s="16" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3665,7 +4216,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3910,7 +4461,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4937,7 +5488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17975,7 +18526,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18606,13 +19157,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -18773,57 +19324,78 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="B26" s="39" t="inlineStr">
+        <is>
+          <t>Phase budget / governance (Jules): owner: Delivery Manager (synthetic), 2026-09-28</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Stamp: built 2026-09-28T10:57:59; sha256 of each cited file</t>
+      <c r="B27" s="39" t="inlineStr">
+        <is>
+          <t>Phase budget / diagrams &amp; design docs (Leonardo): owner: Delivery Manager (synthetic), 2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="39" t="inlineStr">
         <is>
-          <t>_bmad-output/planning-artifacts/architecture/falcon/ARCHITECTURE-SPINE.md  888bd47cdcac</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="39" t="inlineStr">
-        <is>
-          <t>_bmad-output/planning-artifacts/epics.md  68f432fd10b0</t>
+          <t>Phase budget / test design: owner: Delivery Manager (synthetic), 2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="39" t="inlineStr">
-        <is>
-          <t>_bmad-output/specs/SPEC.md  13119f5f0756</t>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Stamp: built 2026-09-28T14:45:51; sha256 of each cited file</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="39" t="inlineStr">
         <is>
-          <t>token_usage/claude_usage.csv  a04b88ac9faf</t>
+          <t>_bmad-output/planning-artifacts/architecture/falcon/ARCHITECTURE-SPINE.md  888bd47cdcac</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="39" t="inlineStr">
         <is>
-          <t>claude-prices.json  0dcde61aa110</t>
+          <t>_bmad-output/planning-artifacts/epics.md  68f432fd10b0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="39" t="inlineStr">
         <is>
-          <t>token_usage/project_timeline.csv  08bf946524c1</t>
+          <t>_bmad-output/specs/SPEC.md  13119f5f0756</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="39" t="inlineStr">
+        <is>
+          <t>token_usage/claude_usage.csv  a04b88ac9faf</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="39" t="inlineStr">
+        <is>
+          <t>claude-prices.json  0dcde61aa110</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="39" t="inlineStr">
+        <is>
+          <t>token_usage/project_timeline.csv  08bf946524c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="39" t="inlineStr">
         <is>
           <t>token_usage/claude_usage_daily.csv  f12be0ce39fb</t>
         </is>
@@ -21060,6 +21632,227 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Phase budgets: Claude API budget and actual per planning phase</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>In USD, at Claude API list prices. The budget each planning phase may spend (test design, governance, diagrams, course corrections ...), set once the epics and sprint plan are done; the epics and sprints carry their own budgets on their sheets. Actual: the phase's Claude cost from the ledger (Claude Usage Detail) once the close-out sheets are in. A control figure: not added to any total. Blue cells are inputs; name a phase as the token ledger does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Claude API budget (USD)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Claude API actual (USD)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Variance (USD)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Variance %</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Cited from</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>governance (Jules)</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="C5" s="14">
+        <f>IF(A5="","",SUMIFS('Claude Usage Detail'!$P$5:$P$19,'Claude Usage Detail'!$B$5:$B$19,A5))</f>
+        <v/>
+      </c>
+      <c r="D5" s="30">
+        <f>IF(OR(A5="",C5=""),"",C5-N(B5))</f>
+        <v/>
+      </c>
+      <c r="E5" s="29">
+        <f>IF(OR(D5="",N(B5)=0),"",C5/B5-1)</f>
+        <v/>
+      </c>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
+          <t>owner: Delivery Manager (synthetic), 2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>diagrams &amp; design docs (Leonardo)</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C6" s="14">
+        <f>IF(A6="","",SUMIFS('Claude Usage Detail'!$P$5:$P$19,'Claude Usage Detail'!$B$5:$B$19,A6))</f>
+        <v/>
+      </c>
+      <c r="D6" s="30">
+        <f>IF(OR(A6="",C6=""),"",C6-N(B6))</f>
+        <v/>
+      </c>
+      <c r="E6" s="29">
+        <f>IF(OR(D6="",N(B6)=0),"",C6/B6-1)</f>
+        <v/>
+      </c>
+      <c r="F6" s="25" t="inlineStr">
+        <is>
+          <t>owner: Delivery Manager (synthetic), 2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>test design</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="C7" s="14">
+        <f>IF(A7="","",SUMIFS('Claude Usage Detail'!$P$5:$P$19,'Claude Usage Detail'!$B$5:$B$19,A7))</f>
+        <v/>
+      </c>
+      <c r="D7" s="30">
+        <f>IF(OR(A7="",C7=""),"",C7-N(B7))</f>
+        <v/>
+      </c>
+      <c r="E7" s="29">
+        <f>IF(OR(D7="",N(B7)=0),"",C7/B7-1)</f>
+        <v/>
+      </c>
+      <c r="F7" s="25" t="inlineStr">
+        <is>
+          <t>owner: Delivery Manager (synthetic), 2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="14">
+        <f>IF(A8="","",SUMIFS('Claude Usage Detail'!$P$5:$P$19,'Claude Usage Detail'!$B$5:$B$19,A8))</f>
+        <v/>
+      </c>
+      <c r="D8" s="30">
+        <f>IF(OR(A8="",C8=""),"",C8-N(B8))</f>
+        <v/>
+      </c>
+      <c r="E8" s="29">
+        <f>IF(OR(D8="",N(B8)=0),"",C8/B8-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="n"/>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="14">
+        <f>IF(A9="","",SUMIFS('Claude Usage Detail'!$P$5:$P$19,'Claude Usage Detail'!$B$5:$B$19,A9))</f>
+        <v/>
+      </c>
+      <c r="D9" s="30">
+        <f>IF(OR(A9="",C9=""),"",C9-N(B9))</f>
+        <v/>
+      </c>
+      <c r="E9" s="29">
+        <f>IF(OR(D9="",N(B9)=0),"",C9/B9-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="14">
+        <f>IF(A10="","",SUMIFS('Claude Usage Detail'!$P$5:$P$19,'Claude Usage Detail'!$B$5:$B$19,A10))</f>
+        <v/>
+      </c>
+      <c r="D10" s="30">
+        <f>IF(OR(A10="",C10=""),"",C10-N(B10))</f>
+        <v/>
+      </c>
+      <c r="E10" s="29">
+        <f>IF(OR(D10="",N(B10)=0),"",C10/B10-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B11" s="18">
+        <f>SUM(B5:B10)</f>
+        <v/>
+      </c>
+      <c r="C11" s="18">
+        <f>SUM(C5:C10)</f>
+        <v/>
+      </c>
+      <c r="D11" s="18">
+        <f>SUM(D5:D10)</f>
+        <v/>
+      </c>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -21237,7 +22030,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21356,7 +22149,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21495,7 +22288,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21620,539 +22413,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
-    <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Dev environment</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Azure retail list prices (pay-as-you-go) in uaenorth, USD, fetched 2026-09-28. Daily cost is the monthly cost spread over the year (x 12 / 365). Blue cells are inputs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Azure service</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>SKU / tier</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Unit price (USD)</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Usage per month</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Monthly cost (USD)</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Daily cost (USD)</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Annual cost (USD)</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>Cited from</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>Price source</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>Environment</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>AKS nodes</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Virtual Machines</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Standard_D4s_v5</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1 Hour</t>
-        </is>
-      </c>
-      <c r="F5" s="35" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>220</v>
-      </c>
-      <c r="I5" s="14">
-        <f>F5*G5*H5*FxRate</f>
-        <v/>
-      </c>
-      <c r="J5" s="14">
-        <f>I5*12/365</f>
-        <v/>
-      </c>
-      <c r="K5" s="14">
-        <f>I5*12</f>
-        <v/>
-      </c>
-      <c r="L5" s="25" t="inlineStr">
-        <is>
-          <t>_bmad-output/planning-artifacts/architecture/falcon/ARCHITECTURE-SPINE.md AD-1</t>
-        </is>
-      </c>
-      <c r="M5" s="25" t="inlineStr">
-        <is>
-          <t>Azure Retail Prices API, Virtual Machines Dsv5 Series / D4s v5, uaenorth, USD per 1 Hour, meterId 75a8da05-74dd-5b32-bb86-4f5cc74cdb60, fetched 2026-09-28</t>
-        </is>
-      </c>
-      <c r="N5" s="25" t="inlineStr">
-        <is>
-          <t>Dev nodes stopped outside working hours</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Dev</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Customer database</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>SQL Database</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>General Purpose Gen5, 2 vCore</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1 vCore Hour</t>
-        </is>
-      </c>
-      <c r="F6" s="35" t="n">
-        <v>0.253</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" s="13">
-        <f>HoursPerMonth</f>
-        <v/>
-      </c>
-      <c r="I6" s="14">
-        <f>F6*G6*H6*FxRate</f>
-        <v/>
-      </c>
-      <c r="J6" s="14">
-        <f>I6*12/365</f>
-        <v/>
-      </c>
-      <c r="K6" s="14">
-        <f>I6*12</f>
-        <v/>
-      </c>
-      <c r="L6" s="25" t="inlineStr">
-        <is>
-          <t>_bmad-output/planning-artifacts/architecture/falcon/ARCHITECTURE-SPINE.md AD-2</t>
-        </is>
-      </c>
-      <c r="M6" s="25" t="inlineStr">
-        <is>
-          <t>Synthetic sample price (not looked up)</t>
-        </is>
-      </c>
-      <c r="N6" s="25" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Dev</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Document storage</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Blob Hot LRS</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1 GB/Month</t>
-        </is>
-      </c>
-      <c r="F7" s="35" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="14">
-        <f>F7*G7*H7*FxRate</f>
-        <v/>
-      </c>
-      <c r="J7" s="14">
-        <f>I7*12/365</f>
-        <v/>
-      </c>
-      <c r="K7" s="14">
-        <f>I7*12</f>
-        <v/>
-      </c>
-      <c r="L7" s="25" t="inlineStr">
-        <is>
-          <t>assumption: 50 GB of test documents</t>
-        </is>
-      </c>
-      <c r="M7" s="25" t="inlineStr">
-        <is>
-          <t>Synthetic sample price (not looked up)</t>
-        </is>
-      </c>
-      <c r="N7" s="25" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Dev</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Secrets</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Key Vault</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>10K operations</t>
-        </is>
-      </c>
-      <c r="F8" s="35" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="14">
-        <f>F8*G8*H8*FxRate</f>
-        <v/>
-      </c>
-      <c r="J8" s="14">
-        <f>I8*12/365</f>
-        <v/>
-      </c>
-      <c r="K8" s="14">
-        <f>I8*12</f>
-        <v/>
-      </c>
-      <c r="L8" s="25" t="inlineStr">
-        <is>
-          <t>_bmad-output/planning-artifacts/architecture/falcon/ARCHITECTURE-SPINE.md AD-5</t>
-        </is>
-      </c>
-      <c r="M8" s="25" t="inlineStr">
-        <is>
-          <t>Synthetic sample price (not looked up)</t>
-        </is>
-      </c>
-      <c r="N8" s="25" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Dev</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Logs and metrics</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Log Analytics</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Pay-as-you-go</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1 GB</t>
-        </is>
-      </c>
-      <c r="F9" s="35" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="14">
-        <f>F9*G9*H9*FxRate</f>
-        <v/>
-      </c>
-      <c r="J9" s="14">
-        <f>I9*12/365</f>
-        <v/>
-      </c>
-      <c r="K9" s="14">
-        <f>I9*12</f>
-        <v/>
-      </c>
-      <c r="L9" s="25" t="inlineStr">
-        <is>
-          <t>_bmad-output/planning-artifacts/architecture/falcon/ARCHITECTURE-SPINE.md AD-5</t>
-        </is>
-      </c>
-      <c r="M9" s="25" t="inlineStr">
-        <is>
-          <t>Synthetic sample price (not looked up)</t>
-        </is>
-      </c>
-      <c r="N9" s="25" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Dev</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="15" t="n"/>
-      <c r="I10" s="14">
-        <f>IF(F10="","",F10*G10*H10*FxRate)</f>
-        <v/>
-      </c>
-      <c r="J10" s="14">
-        <f>IF(I10="","",I10*12/365)</f>
-        <v/>
-      </c>
-      <c r="K10" s="14">
-        <f>IF(I10="","",I10*12)</f>
-        <v/>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Dev</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="15" t="n"/>
-      <c r="I11" s="14">
-        <f>IF(F11="","",F11*G11*H11*FxRate)</f>
-        <v/>
-      </c>
-      <c r="J11" s="14">
-        <f>IF(I11="","",I11*12/365)</f>
-        <v/>
-      </c>
-      <c r="K11" s="14">
-        <f>IF(I11="","",I11*12)</f>
-        <v/>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Dev</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="F12" s="15" t="n"/>
-      <c r="G12" s="15" t="n"/>
-      <c r="H12" s="15" t="n"/>
-      <c r="I12" s="14">
-        <f>IF(F12="","",F12*G12*H12*FxRate)</f>
-        <v/>
-      </c>
-      <c r="J12" s="14">
-        <f>IF(I12="","",I12*12/365)</f>
-        <v/>
-      </c>
-      <c r="K12" s="14">
-        <f>IF(I12="","",I12*12)</f>
-        <v/>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Dev</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
-      <c r="G13" s="16" t="n"/>
-      <c r="H13" s="16" t="n"/>
-      <c r="I13" s="18">
-        <f>SUM(I5:I12)</f>
-        <v/>
-      </c>
-      <c r="J13" s="18">
-        <f>SUM(J5:J12)</f>
-        <v/>
-      </c>
-      <c r="K13" s="18">
-        <f>SUM(K5:K12)</f>
-        <v/>
-      </c>
-      <c r="L13" s="16" t="n"/>
-      <c r="M13" s="16" t="n"/>
-      <c r="N13" s="16" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/skills/agent-scrooge/assets/examples/falcon-portal/falcon-portal.xlsx
+++ b/skills/agent-scrooge/assets/examples/falcon-portal/falcon-portal.xlsx
@@ -4928,7 +4928,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>diagrams &amp; design docs (Leonardo)</t>
+          <t>architecture docs (Da Vinci)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -6305,7 +6305,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>diagrams &amp; design docs (Leonardo)</t>
+          <t>architecture docs (Da Vinci)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -6517,7 +6517,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>diagrams &amp; design docs (Leonardo)</t>
+          <t>architecture docs (Da Vinci)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>diagrams &amp; design docs (Leonardo)</t>
+          <t>architecture docs (Da Vinci)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -19334,7 +19334,7 @@
     <row r="27">
       <c r="B27" s="39" t="inlineStr">
         <is>
-          <t>Phase budget / diagrams &amp; design docs (Leonardo): owner: Delivery Manager (synthetic), 2026-09-28</t>
+          <t>Phase budget / architecture docs (Da Vinci): owner: Delivery Manager (synthetic), 2026-09-28</t>
         </is>
       </c>
     </row>
@@ -19348,7 +19348,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Stamp: built 2026-09-28T14:45:51; sha256 of each cited file</t>
+          <t>Stamp: built 2026-09-28T15:18:38; sha256 of each cited file</t>
         </is>
       </c>
     </row>
@@ -19376,7 +19376,7 @@
     <row r="34">
       <c r="B34" s="39" t="inlineStr">
         <is>
-          <t>token_usage/claude_usage.csv  a04b88ac9faf</t>
+          <t>token_usage/claude_usage.csv  e972364ca316</t>
         </is>
       </c>
     </row>
@@ -19397,7 +19397,7 @@
     <row r="37">
       <c r="B37" s="39" t="inlineStr">
         <is>
-          <t>token_usage/claude_usage_daily.csv  f12be0ce39fb</t>
+          <t>token_usage/claude_usage_daily.csv  2a1ddfa62ec0</t>
         </is>
       </c>
     </row>
@@ -21719,7 +21719,7 @@
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>diagrams &amp; design docs (Leonardo)</t>
+          <t>architecture docs (Da Vinci)</t>
         </is>
       </c>
       <c r="B6" s="27" t="n">
